--- a/etl/sources/Sports_Framework_v12.xlsx
+++ b/etl/sources/Sports_Framework_v12.xlsx
@@ -10241,7 +10241,8 @@
       </c>
       <c r="F40" s="213" t="inlineStr">
         <is>
-          <t>All formats: aerobic engine and recovery days</t>
+          <t>95–100% of race time
+(All formats: D-001 is the umbrella discipline; uphill / downhill / scrambling rows below sub-allocate within trail running. Aerobic engine and recovery days.)</t>
         </is>
       </c>
       <c r="G40" s="213" t="inlineStr">
@@ -10444,7 +10445,8 @@
       </c>
       <c r="F44" s="215" t="inlineStr">
         <is>
-          <t>All categories: aerobic engine and recovery days</t>
+          <t>95–100% of race time
+(All categories: D-001 is the umbrella discipline; uphill / downhill / nav rows below sub-allocate. Aerobic engine and recovery days.)</t>
         </is>
       </c>
       <c r="G44" s="215" t="inlineStr">
@@ -11166,8 +11168,8 @@
       </c>
       <c r="F58" s="203" t="inlineStr">
         <is>
-          <t>Century (100 mi): 4-7 hrs
-Ultra-endurance road (200+ mi): 8-16+ hrs</t>
+          <t>95–100% of race time
+(Century (100 mi): 4-7 hrs; Ultra-endurance road (200+ mi): 8-16+ hrs. Mono-discipline for road-format athletes.)</t>
         </is>
       </c>
       <c r="G58" s="203" t="inlineStr">
@@ -11222,9 +11224,8 @@
       </c>
       <c r="F59" s="203" t="inlineStr">
         <is>
-          <t>50-mi gravel: 3-5 hrs
-Century gravel: 5-8 hrs
-Unbound 200 (ultra-gravel): 10-16 hrs for most riders</t>
+          <t>95–100% of race time
+(50-mi gravel: 3-5 hrs; Century gravel: 5-8 hrs; Unbound 200 (ultra-gravel): 10-16 hrs. Mono-discipline for gravel-format athletes.)</t>
         </is>
       </c>
       <c r="G59" s="203" t="inlineStr">
@@ -11285,9 +11286,8 @@
       </c>
       <c r="F60" s="203" t="inlineStr">
         <is>
-          <t>10km TT: ~12-20 min
-25-mile TT: ~55-75 min
-100km TT: ~2.5-3.5 hrs</t>
+          <t>95–100% of race time
+(10km TT: ~12-20 min; 25-mile TT: ~55-75 min; 100km TT: ~2.5-3.5 hrs. Mono-discipline for TT-format athletes.)</t>
         </is>
       </c>
       <c r="G60" s="203" t="inlineStr">
@@ -11349,9 +11349,8 @@
       </c>
       <c r="F61" s="203" t="inlineStr">
         <is>
-          <t>XCO (Olympic): 1.5-2 hrs (circuit laps)
-XCS (Short Track): 30-45 min
-XCM (Marathon): 3-7 hrs</t>
+          <t>95–100% of race time
+(XCO Olympic: 1.5-2 hrs circuit laps; XCS Short Track: 30-45 min; XCM Marathon: 3-7 hrs. Mono-discipline for XC-MTB-format athletes.)</t>
         </is>
       </c>
       <c r="G61" s="203" t="inlineStr">
@@ -11416,9 +11415,8 @@
       </c>
       <c r="F62" s="203" t="inlineStr">
         <is>
-          <t>Timed stages: 3-15 min each
-Total race day incl. transfers: 4-8 hrs
-Typically 3-6 timed stages per day</t>
+          <t>95–100% of race time
+(Timed stages: 3-15 min each; Total race day incl. transfers: 4-8 hrs. Mono-discipline for Enduro-format athletes; aggregate time on bike.)</t>
         </is>
       </c>
       <c r="G62" s="203" t="inlineStr">
@@ -14245,8 +14243,8 @@
   <mergeCells count="16">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="A1:F1"/>
